--- a/samples/corpus/full/chantiers/nacrines/3-execution/situation/2026-03-31_situation-n4.xlsx
+++ b/samples/corpus/full/chantiers/nacrines/3-execution/situation/2026-03-31_situation-n4.xlsx
@@ -513,7 +513,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Lot 2 - Nettoyage, traitement des fissures et peinture minérale des quatre façades</t>
+          <t>Lot 2 - Façades sud et est, nez de balcons, sous-faces et soubassements : nettoyage, traitement des fissures et peinture minérale</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
